--- a/4.evidence/FCRP/ConsolidationEntries_NonStandard_DeliberationMemo_FY2025.xlsx
+++ b/4.evidence/FCRP/ConsolidationEntries_NonStandard_DeliberationMemo_FY2025.xlsx
@@ -455,6 +455,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -678,7 +679,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TPT(タイ)の期末為替レート改定影響(3.80→4.05円/THB)</t>
+          <t>DAT(タイ)の期末為替レート改定影響(3.80→4.05円/THB)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
